--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -41157,7 +41157,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>410 partidos (2025-26: 380 partidos, 2026-27: 30 partidos). 28 columnas. Cargado el 12/09/2026.</t>
+          <t>410 partidos (2025-26: 380 partidos, 2026-27: 30 partidos). 28 columnas. Cargado el 13/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -41157,7 +41157,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>410 partidos (2025-26: 380 partidos, 2026-27: 30 partidos). 28 columnas. Cargado el 13/09/2026.</t>
+          <t>410 partidos (2025-26: 380 partidos, 2026-27: 30 partidos). 28 columnas. Cargado el 14/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -11,7 +11,7 @@
     <sheet name="diccionario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$411</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$421</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB411"/>
+  <dimension ref="A1:AB421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -40799,8 +40799,988 @@
         <v>0</v>
       </c>
     </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="F412" s="2" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I412" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J412" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K412" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L412" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M412" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N412" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O412" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P412" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q412" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="R412" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="S412" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T412" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="U412" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V412" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W412" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X412" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y412" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z412" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA412" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB412" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F413" s="2" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I413" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J413" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K413" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L413" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M413" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O413" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P413" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q413" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R413" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="S413" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="V413" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="W413" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="X413" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y413" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z413" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA413" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB413" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F414" s="2" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I414" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J414" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K414" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L414" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M414" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O414" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P414" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q414" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="R414" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="S414" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V414" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W414" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="X414" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y414" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z414" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA414" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB414" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I415" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J415" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K415" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L415" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M415" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O415" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P415" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q415" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="R415" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S415" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V415" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W415" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X415" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y415" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z415" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA415" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB415" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="H416" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I416" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J416" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K416" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L416" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M416" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N416" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O416" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P416" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q416" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="R416" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="S416" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T416" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="U416" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V416" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W416" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X416" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y416" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z416" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA416" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB416" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="D417" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F417" s="2" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="H417" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I417" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J417" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K417" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L417" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M417" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N417" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O417" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P417" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q417" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="R417" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S417" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T417" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U417" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V417" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W417" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="X417" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y417" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z417" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA417" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB417" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="D418" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="F418" s="2" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="H418" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I418" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J418" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K418" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L418" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M418" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N418" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O418" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P418" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q418" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="R418" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="S418" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T418" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U418" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V418" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="W418" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="X418" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y418" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z418" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA418" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB418" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C419" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="D419" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E419" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F419" s="2" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="G419" s="2" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="H419" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I419" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J419" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K419" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L419" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M419" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N419" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O419" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P419" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q419" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="R419" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="S419" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T419" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U419" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="V419" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W419" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="X419" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y419" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z419" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA419" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB419" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B420" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="D420" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F420" s="2" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="H420" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I420" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J420" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K420" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L420" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M420" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N420" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O420" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P420" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q420" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="R420" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="S420" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T420" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U420" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V420" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="W420" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="X420" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y420" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z420" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA420" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB420" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="D421" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="F421" s="2" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="G421" s="2" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="H421" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I421" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J421" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K421" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L421" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M421" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N421" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O421" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P421" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q421" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="R421" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="S421" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="T421" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U421" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V421" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W421" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X421" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y421" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z421" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA421" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB421" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB411"/>
+  <autoFilter ref="A1:AB421"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -41157,7 +42137,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>410 partidos (2025-26: 380 partidos, 2026-27: 30 partidos). 28 columnas. Cargado el 14/09/2026.</t>
+          <t>420 partidos (2025-26: 380 partidos, 2026-27: 40 partidos). 28 columnas. Cargado el 15/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -42137,7 +42137,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>420 partidos (2025-26: 380 partidos, 2026-27: 40 partidos). 28 columnas. Cargado el 15/09/2026.</t>
+          <t>420 partidos (2025-26: 380 partidos, 2026-27: 40 partidos). 28 columnas. Cargado el 16/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -42137,7 +42137,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>420 partidos (2025-26: 380 partidos, 2026-27: 40 partidos). 28 columnas. Cargado el 16/09/2026.</t>
+          <t>420 partidos (2025-26: 380 partidos, 2026-27: 40 partidos). 28 columnas. Cargado el 18/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -42137,7 +42137,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>420 partidos (2025-26: 380 partidos, 2026-27: 40 partidos). 28 columnas. Cargado el 18/09/2026.</t>
+          <t>420 partidos (2025-26: 380 partidos, 2026-27: 40 partidos). 28 columnas. Cargado el 19/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -42137,7 +42137,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>420 partidos (2025-26: 380 partidos, 2026-27: 40 partidos). 28 columnas. Cargado el 19/09/2026.</t>
+          <t>420 partidos (2025-26: 380 partidos, 2026-27: 40 partidos). 28 columnas. Cargado el 20/09/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -11,7 +11,7 @@
     <sheet name="diccionario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$421</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$441</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB421"/>
+  <dimension ref="A1:AB441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -41779,8 +41779,1968 @@
         <v>0</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="D422" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="F422" s="2" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="G422" s="2" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="H422" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I422" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J422" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K422" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L422" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M422" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N422" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O422" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P422" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q422" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="R422" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S422" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T422" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U422" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V422" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W422" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="X422" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y422" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z422" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA422" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB422" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="D423" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F423" s="2" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="H423" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I423" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J423" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K423" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L423" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M423" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N423" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O423" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P423" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q423" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="R423" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="S423" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T423" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U423" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V423" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W423" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="X423" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y423" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z423" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA423" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB423" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="H424" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I424" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J424" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K424" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L424" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M424" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N424" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O424" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P424" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q424" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="R424" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S424" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T424" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U424" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="V424" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W424" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X424" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y424" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z424" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA424" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB424" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="D425" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F425" s="2" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="H425" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I425" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J425" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K425" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L425" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M425" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N425" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O425" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P425" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q425" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R425" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="S425" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T425" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U425" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V425" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W425" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="X425" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y425" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z425" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA425" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB425" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
+        </is>
+      </c>
+      <c r="D426" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="F426" s="2" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="G426" s="2" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="H426" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I426" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J426" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K426" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L426" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M426" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N426" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O426" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P426" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q426" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R426" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="S426" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T426" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U426" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V426" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W426" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X426" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y426" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z426" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA426" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB426" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I427" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J427" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K427" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L427" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M427" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N427" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O427" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P427" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q427" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R427" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="S427" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T427" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U427" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V427" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W427" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X427" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y427" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z427" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA427" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB427" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="H428" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I428" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J428" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K428" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L428" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M428" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N428" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O428" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P428" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q428" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="R428" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="S428" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T428" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U428" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V428" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="W428" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="X428" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y428" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z428" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA428" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB428" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="D429" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F429" s="2" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="G429" s="2" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="H429" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I429" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J429" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K429" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L429" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M429" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N429" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O429" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P429" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q429" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R429" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="S429" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T429" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U429" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V429" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W429" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X429" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y429" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z429" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA429" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB429" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="G430" s="2" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="H430" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I430" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J430" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K430" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L430" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M430" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N430" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O430" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P430" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q430" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="R430" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S430" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T430" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U430" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V430" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W430" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X430" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y430" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z430" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA430" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB430" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="F431" s="2" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="H431" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I431" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J431" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K431" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L431" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M431" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N431" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O431" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P431" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q431" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="R431" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="S431" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T431" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U431" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V431" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W431" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X431" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y431" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z431" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA431" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB431" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F432" s="2" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="H432" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I432" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J432" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K432" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L432" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M432" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N432" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O432" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P432" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q432" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="R432" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="S432" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T432" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U432" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V432" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W432" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X432" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y432" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z432" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA432" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB432" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="G433" s="2" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="H433" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I433" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J433" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K433" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L433" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M433" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N433" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O433" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P433" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q433" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="R433" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S433" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T433" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U433" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V433" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W433" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="X433" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y433" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z433" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA433" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB433" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="F434" s="2" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="G434" s="2" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="H434" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I434" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J434" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K434" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L434" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M434" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N434" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O434" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P434" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q434" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="R434" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="S434" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T434" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U434" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V434" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W434" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="X434" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y434" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z434" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA434" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB434" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="D435" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="F435" s="2" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="G435" s="2" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="H435" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I435" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J435" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K435" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L435" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M435" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N435" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O435" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P435" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q435" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="R435" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S435" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T435" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U435" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V435" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W435" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X435" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y435" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z435" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA435" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB435" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="H436" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I436" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J436" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K436" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L436" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M436" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N436" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O436" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P436" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q436" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R436" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="S436" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T436" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U436" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V436" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W436" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X436" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y436" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z436" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA436" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB436" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F437" s="2" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="H437" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I437" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J437" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K437" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L437" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M437" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N437" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O437" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P437" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q437" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="R437" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S437" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T437" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U437" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V437" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W437" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X437" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y437" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z437" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA437" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB437" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="D438" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F438" s="2" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="G438" s="2" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="H438" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I438" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J438" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K438" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L438" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M438" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N438" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O438" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P438" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q438" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="R438" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="S438" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T438" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U438" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V438" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W438" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="X438" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y438" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z438" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA438" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB438" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="D439" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="F439" s="2" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="G439" s="2" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="H439" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I439" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J439" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K439" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L439" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M439" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N439" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O439" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P439" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q439" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R439" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="S439" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T439" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="U439" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V439" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="W439" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="X439" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y439" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z439" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA439" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB439" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="G440" s="2" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="H440" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I440" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J440" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K440" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L440" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M440" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N440" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O440" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P440" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q440" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="R440" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="S440" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="T440" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U440" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="V440" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="W440" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X440" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y440" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z440" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA440" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB440" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B441" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="F441" s="2" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="G441" s="2" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="H441" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I441" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J441" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K441" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L441" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M441" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N441" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O441" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P441" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q441" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="R441" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="S441" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T441" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U441" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V441" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W441" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="X441" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y441" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z441" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA441" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB441" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB421"/>
+  <autoFilter ref="A1:AB441"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -42137,7 +44097,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>420 partidos (2025-26: 380 partidos, 2026-27: 40 partidos). 28 columnas. Cargado el 20/09/2026.</t>
+          <t>440 partidos (2025-26: 380 partidos, 2026-27: 60 partidos). 28 columnas. Cargado el 17/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -44097,7 +44097,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>440 partidos (2025-26: 380 partidos, 2026-27: 60 partidos). 28 columnas. Cargado el 17/10/2026.</t>
+          <t>440 partidos (2025-26: 380 partidos, 2026-27: 60 partidos). 28 columnas. Cargado el 18/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -44097,7 +44097,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>440 partidos (2025-26: 380 partidos, 2026-27: 60 partidos). 28 columnas. Cargado el 18/10/2026.</t>
+          <t>440 partidos (2025-26: 380 partidos, 2026-27: 60 partidos). 28 columnas. Cargado el 19/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -11,7 +11,7 @@
     <sheet name="diccionario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$441</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$451</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB441"/>
+  <dimension ref="A1:AB451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -43739,8 +43739,988 @@
         <v>0</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B442" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="F442" s="2" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="H442" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I442" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J442" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K442" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L442" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M442" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N442" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="O442" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P442" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q442" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="R442" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="S442" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="T442" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U442" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V442" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W442" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="X442" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y442" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z442" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA442" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB442" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B443" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="D443" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F443" s="2" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="G443" s="2" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="H443" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I443" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J443" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K443" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L443" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M443" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N443" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O443" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P443" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q443" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="R443" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="S443" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T443" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="U443" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V443" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="W443" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="X443" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y443" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z443" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA443" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB443" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B444" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F444" s="2" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="H444" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I444" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J444" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K444" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L444" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M444" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N444" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O444" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P444" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q444" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="R444" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="S444" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T444" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U444" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V444" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W444" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="X444" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y444" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z444" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA444" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB444" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B445" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="D445" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="F445" s="2" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="G445" s="2" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="H445" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I445" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J445" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K445" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L445" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M445" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N445" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O445" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P445" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q445" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="R445" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S445" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T445" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U445" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V445" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W445" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X445" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y445" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z445" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA445" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB445" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B446" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="F446" s="2" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="G446" s="2" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="H446" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I446" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J446" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K446" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L446" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M446" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N446" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O446" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P446" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q446" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="R446" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="S446" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T446" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="U446" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V446" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W446" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X446" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y446" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z446" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA446" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB446" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B447" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="D447" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F447" s="2" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="G447" s="2" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="H447" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I447" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J447" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K447" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L447" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M447" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N447" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O447" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P447" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q447" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="R447" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="S447" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T447" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U447" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="V447" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W447" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="X447" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y447" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z447" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA447" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB447" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B448" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="D448" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F448" s="2" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="G448" s="2" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="H448" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I448" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J448" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K448" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L448" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M448" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N448" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O448" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P448" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q448" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="R448" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="S448" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T448" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U448" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V448" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W448" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="X448" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y448" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z448" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA448" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB448" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B449" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="D449" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="F449" s="2" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="G449" s="2" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="H449" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I449" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J449" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K449" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L449" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M449" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N449" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O449" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P449" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q449" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="R449" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S449" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T449" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U449" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V449" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="W449" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="X449" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y449" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z449" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA449" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB449" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B450" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="D450" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F450" s="2" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="G450" s="2" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="H450" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I450" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J450" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K450" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L450" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M450" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N450" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O450" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P450" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q450" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="R450" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="S450" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T450" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U450" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V450" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="W450" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X450" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y450" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z450" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA450" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB450" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B451" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="D451" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="F451" s="2" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="G451" s="2" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="H451" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I451" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J451" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K451" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L451" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M451" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N451" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O451" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P451" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q451" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="R451" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S451" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T451" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U451" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V451" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W451" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="X451" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y451" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z451" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA451" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB451" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB441"/>
+  <autoFilter ref="A1:AB451"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -44097,7 +45077,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>440 partidos (2025-26: 380 partidos, 2026-27: 60 partidos). 28 columnas. Cargado el 19/10/2026.</t>
+          <t>450 partidos (2025-26: 380 partidos, 2026-27: 70 partidos). 28 columnas. Cargado el 20/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -45077,7 +45077,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>450 partidos (2025-26: 380 partidos, 2026-27: 70 partidos). 28 columnas. Cargado el 20/10/2026.</t>
+          <t>450 partidos (2025-26: 380 partidos, 2026-27: 70 partidos). 28 columnas. Cargado el 21/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -45077,7 +45077,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>450 partidos (2025-26: 380 partidos, 2026-27: 70 partidos). 28 columnas. Cargado el 21/10/2026.</t>
+          <t>450 partidos (2025-26: 380 partidos, 2026-27: 70 partidos). 28 columnas. Cargado el 22/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -45077,7 +45077,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>450 partidos (2025-26: 380 partidos, 2026-27: 70 partidos). 28 columnas. Cargado el 22/10/2026.</t>
+          <t>450 partidos (2025-26: 380 partidos, 2026-27: 70 partidos). 28 columnas. Cargado el 21/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -45077,7 +45077,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>450 partidos (2025-26: 380 partidos, 2026-27: 70 partidos). 28 columnas. Cargado el 22/10/2026.</t>
+          <t>450 partidos (2025-26: 380 partidos, 2026-27: 70 partidos). 28 columnas. Cargado el 23/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -45077,7 +45077,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>450 partidos (2025-26: 380 partidos, 2026-27: 70 partidos). 28 columnas. Cargado el 23/10/2026.</t>
+          <t>450 partidos (2025-26: 380 partidos, 2026-27: 70 partidos). 28 columnas. Cargado el 24/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -45077,7 +45077,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>450 partidos (2025-26: 380 partidos, 2026-27: 70 partidos). 28 columnas. Cargado el 24/10/2026.</t>
+          <t>450 partidos (2025-26: 380 partidos, 2026-27: 70 partidos). 28 columnas. Cargado el 25/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -45077,7 +45077,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>450 partidos (2025-26: 380 partidos, 2026-27: 70 partidos). 28 columnas. Cargado el 25/10/2026.</t>
+          <t>450 partidos (2025-26: 380 partidos, 2026-27: 70 partidos). 28 columnas. Cargado el 26/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -11,7 +11,7 @@
     <sheet name="diccionario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$451</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$461</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB451"/>
+  <dimension ref="A1:AB461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -44719,8 +44719,988 @@
         <v>0</v>
       </c>
     </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B452" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="D452" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="F452" s="2" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="G452" s="2" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="H452" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I452" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J452" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K452" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L452" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M452" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N452" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O452" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P452" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q452" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R452" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="S452" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T452" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U452" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V452" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W452" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="X452" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y452" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z452" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA452" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB452" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B453" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C453" s="2" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="D453" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F453" s="2" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="G453" s="2" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="H453" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I453" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J453" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K453" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L453" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M453" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N453" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O453" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P453" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q453" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R453" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="S453" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T453" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U453" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V453" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W453" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="X453" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y453" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z453" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA453" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB453" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B454" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F454" s="2" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="G454" s="2" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="H454" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I454" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J454" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K454" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L454" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M454" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N454" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O454" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P454" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q454" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="R454" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="S454" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T454" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U454" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V454" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W454" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X454" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y454" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z454" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA454" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB454" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B455" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F455" s="2" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="G455" s="2" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="H455" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I455" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J455" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K455" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L455" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M455" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N455" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O455" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P455" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q455" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="R455" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="S455" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="T455" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U455" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V455" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="W455" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="X455" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y455" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z455" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA455" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB455" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="D456" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="F456" s="2" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="G456" s="2" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="H456" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I456" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J456" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K456" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L456" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M456" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N456" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O456" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P456" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q456" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="R456" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="S456" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T456" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U456" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="V456" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W456" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="X456" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y456" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z456" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA456" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB456" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B457" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C457" s="2" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="D457" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="F457" s="2" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="G457" s="2" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="H457" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I457" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J457" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K457" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L457" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M457" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N457" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O457" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P457" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q457" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="R457" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="S457" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="T457" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U457" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V457" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W457" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="X457" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y457" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z457" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA457" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB457" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F458" s="2" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="G458" s="2" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="H458" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I458" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J458" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K458" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L458" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M458" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N458" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="O458" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P458" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q458" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="R458" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="S458" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="T458" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="U458" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="V458" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="W458" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="X458" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y458" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z458" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA458" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB458" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B459" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="D459" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E459" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F459" s="2" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="G459" s="2" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="H459" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I459" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J459" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K459" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L459" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M459" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N459" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O459" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P459" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q459" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="R459" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="S459" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T459" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U459" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V459" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="W459" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="X459" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y459" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z459" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA459" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB459" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F460" s="2" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="H460" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I460" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J460" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K460" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L460" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M460" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N460" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O460" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P460" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q460" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="R460" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S460" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T460" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U460" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V460" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W460" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X460" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y460" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z460" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA460" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB460" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B461" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="D461" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E461" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="F461" s="2" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="G461" s="2" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="H461" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I461" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J461" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K461" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L461" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M461" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N461" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O461" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P461" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q461" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="R461" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="S461" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T461" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U461" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V461" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W461" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X461" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y461" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z461" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA461" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB461" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB451"/>
+  <autoFilter ref="A1:AB461"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -45077,7 +46057,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>450 partidos (2025-26: 380 partidos, 2026-27: 70 partidos). 28 columnas. Cargado el 26/10/2026.</t>
+          <t>460 partidos (2025-26: 380 partidos, 2026-27: 80 partidos). 28 columnas. Cargado el 27/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -46057,7 +46057,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>460 partidos (2025-26: 380 partidos, 2026-27: 80 partidos). 28 columnas. Cargado el 27/10/2026.</t>
+          <t>460 partidos (2025-26: 380 partidos, 2026-27: 80 partidos). 28 columnas. Cargado el 28/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -11,7 +11,7 @@
     <sheet name="diccionario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$461</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$469</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB461"/>
+  <dimension ref="A1:AB469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -45699,8 +45699,792 @@
         <v>0</v>
       </c>
     </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>27/10/2026</t>
+        </is>
+      </c>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="G462" s="2" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="H462" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I462" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J462" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K462" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L462" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M462" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N462" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="O462" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P462" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q462" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="R462" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="S462" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T462" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U462" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V462" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W462" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="X462" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y462" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z462" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA462" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB462" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B463" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>27/10/2026</t>
+        </is>
+      </c>
+      <c r="D463" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="F463" s="2" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="G463" s="2" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="H463" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I463" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J463" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K463" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L463" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M463" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N463" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O463" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P463" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q463" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="R463" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="S463" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T463" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U463" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V463" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="W463" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="X463" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y463" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z463" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA463" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB463" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>27/10/2026</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="F464" s="2" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="G464" s="2" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="H464" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I464" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J464" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K464" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L464" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M464" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N464" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O464" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P464" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q464" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="R464" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="S464" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T464" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U464" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V464" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W464" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X464" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y464" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z464" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA464" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB464" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B465" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C465" s="2" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="D465" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E465" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F465" s="2" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="G465" s="2" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="H465" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I465" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J465" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K465" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L465" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M465" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N465" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O465" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P465" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q465" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="R465" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S465" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T465" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U465" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V465" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W465" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X465" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y465" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z465" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA465" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB465" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="H466" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I466" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J466" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K466" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L466" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M466" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N466" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O466" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P466" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q466" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="R466" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S466" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T466" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U466" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V466" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W466" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="X466" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y466" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z466" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA466" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB466" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B467" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F467" s="2" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="G467" s="2" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="H467" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I467" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J467" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K467" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L467" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M467" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N467" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O467" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P467" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q467" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="R467" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="S467" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T467" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U467" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V467" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W467" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="X467" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y467" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z467" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA467" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB467" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="G468" s="2" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="H468" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I468" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J468" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K468" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L468" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M468" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N468" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O468" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P468" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q468" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="R468" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="S468" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T468" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U468" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V468" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="W468" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="X468" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y468" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z468" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA468" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB468" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B469" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="D469" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E469" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="F469" s="2" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="G469" s="2" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="H469" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I469" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J469" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K469" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L469" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M469" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N469" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O469" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P469" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q469" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="R469" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="S469" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T469" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U469" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V469" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W469" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="X469" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y469" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z469" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA469" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB469" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB461"/>
+  <autoFilter ref="A1:AB469"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -46057,7 +46841,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>460 partidos (2025-26: 380 partidos, 2026-27: 80 partidos). 28 columnas. Cargado el 28/10/2026.</t>
+          <t>468 partidos (2025-26: 380 partidos, 2026-27: 88 partidos). 28 columnas. Cargado el 29/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -11,7 +11,7 @@
     <sheet name="diccionario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$469</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$471</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB469"/>
+  <dimension ref="A1:AB471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -46483,8 +46483,200 @@
         <v>0</v>
       </c>
     </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="D470" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F470" s="2" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="G470" s="2" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="H470" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I470" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J470" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K470" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L470" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M470" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N470" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O470" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P470" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q470" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="R470" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="S470" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="T470" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U470" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V470" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W470" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X470" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y470" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z470" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA470" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB470" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B471" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="D471" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="F471" s="2" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="G471" s="2" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="H471" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I471" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J471" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K471" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L471" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M471" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N471" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O471" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P471" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q471" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="R471" s="2" t="n"/>
+      <c r="S471" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T471" s="2" t="n"/>
+      <c r="U471" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="V471" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W471" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X471" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y471" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z471" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA471" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB471" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB469"/>
+  <autoFilter ref="A1:AB471"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -46841,7 +47033,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>468 partidos (2025-26: 380 partidos, 2026-27: 88 partidos). 28 columnas. Cargado el 29/10/2026.</t>
+          <t>470 partidos (2025-26: 380 partidos, 2026-27: 90 partidos). 28 columnas. Cargado el 29/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -11,7 +11,7 @@
     <sheet name="diccionario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$471</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'partidos'!$A$1:$AB$469</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB471"/>
+  <dimension ref="A1:AB469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -46483,200 +46483,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470">
-      <c r="A470" s="2" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="B470" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="C470" s="2" t="inlineStr">
-        <is>
-          <t>29/10/2026</t>
-        </is>
-      </c>
-      <c r="D470" s="2" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="E470" s="2" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="F470" s="2" t="inlineStr">
-        <is>
-          <t>Frosinone</t>
-        </is>
-      </c>
-      <c r="G470" s="2" t="inlineStr">
-        <is>
-          <t>Lecce</t>
-        </is>
-      </c>
-      <c r="H470" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I470" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J470" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K470" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L470" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M470" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N470" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="O470" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P470" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q470" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="R470" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="S470" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="T470" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="U470" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="V470" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="W470" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="X470" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y470" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z470" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA470" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB470" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" s="2" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="B471" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="C471" s="2" t="inlineStr">
-        <is>
-          <t>29/10/2026</t>
-        </is>
-      </c>
-      <c r="D471" s="2" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="E471" s="2" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="F471" s="2" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="G471" s="2" t="inlineStr">
-        <is>
-          <t>Atalanta</t>
-        </is>
-      </c>
-      <c r="H471" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I471" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J471" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K471" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L471" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M471" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N471" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O471" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P471" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q471" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="R471" s="2" t="n"/>
-      <c r="S471" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="T471" s="2" t="n"/>
-      <c r="U471" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="V471" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="W471" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="X471" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y471" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z471" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA471" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB471" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AB471"/>
+  <autoFilter ref="A1:AB469"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -47033,7 +46841,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>470 partidos (2025-26: 380 partidos, 2026-27: 90 partidos). 28 columnas. Cargado el 29/10/2026.</t>
+          <t>468 partidos (2025-26: 380 partidos, 2026-27: 88 partidos). 28 columnas. Cargado el 29/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -47033,7 +47033,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>470 partidos (2025-26: 380 partidos, 2026-27: 90 partidos). 28 columnas. Cargado el 29/10/2026.</t>
+          <t>470 partidos (2025-26: 380 partidos, 2026-27: 90 partidos). 28 columnas. Cargado el 30/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">

--- a/datos/bbdd_seriea.xlsx
+++ b/datos/bbdd_seriea.xlsx
@@ -47033,7 +47033,7 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>470 partidos (2025-26: 380 partidos, 2026-27: 90 partidos). 28 columnas. Cargado el 30/10/2026.</t>
+          <t>470 partidos (2025-26: 380 partidos, 2026-27: 90 partidos). 28 columnas. Cargado el 31/10/2026.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
